--- a/data/FluTables.xlsx
+++ b/data/FluTables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christopher.johnson\Documents\GitHub\flu\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CC6A04-718B-46C6-BF12-ECFA6239C250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28A349-6DB4-436E-8CBE-DFE992169005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="588" windowWidth="21600" windowHeight="11388" xr2:uid="{11A36013-8756-48B6-B10C-B88575A86A49}"/>
+    <workbookView xWindow="28680" yWindow="2460" windowWidth="29040" windowHeight="15840" xr2:uid="{11A36013-8756-48B6-B10C-B88575A86A49}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="60">
   <si>
     <t>Max</t>
   </si>
@@ -132,17 +132,203 @@
   </si>
   <si>
     <t>Std</t>
+  </si>
+  <si>
+    <t>RNN2-Lin1</t>
+  </si>
+  <si>
+    <t>RNN2-Lin2</t>
+  </si>
+  <si>
+    <t>GRU1-Lin1</t>
+  </si>
+  <si>
+    <t>GRU2-Lin2</t>
+  </si>
+  <si>
+    <t>LSTM2-Lin1</t>
+  </si>
+  <si>
+    <t>LSTM1-Lin1</t>
+  </si>
+  <si>
+    <t>LSTM2-Lin2</t>
+  </si>
+  <si>
+    <t>LSTM1-Lin2</t>
+  </si>
+  <si>
+    <t>RNN1-Lin2</t>
+  </si>
+  <si>
+    <t>GRU1-Lin2</t>
+  </si>
+  <si>
+    <t>22-23</t>
+  </si>
+  <si>
+    <t>23-24</t>
+  </si>
+  <si>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Gam1</t>
+  </si>
+  <si>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Gam2</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>Err</t>
+  </si>
+  <si>
+    <t>Season 23-24</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Г</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Г</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Г</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>adj</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +354,58 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -177,7 +415,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -185,18 +423,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -205,13 +461,78 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -235,7 +556,52 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -275,65 +641,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -373,84 +681,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -471,25 +701,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -509,7 +721,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -529,28 +741,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -624,27 +814,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -683,6 +854,162 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -698,21 +1025,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F15C92B-7033-4A99-B09C-6CF49AEAF9BE}" name="Table1" displayName="Table1" ref="I3:M14" totalsRowCount="1" headerRowDxfId="21" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F15C92B-7033-4A99-B09C-6CF49AEAF9BE}" name="Table1" displayName="Table1" ref="I3:M14" totalsRowCount="1" headerRowDxfId="0" dataDxfId="23">
   <autoFilter ref="I3:M13" xr:uid="{5F15C92B-7033-4A99-B09C-6CF49AEAF9BE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AF8A3B3E-9245-4703-A4D6-DA7EDF18BA10}" name="Model" totalsRowLabel="Mean" dataDxfId="12" totalsRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{42978F44-899C-47DE-A9F1-9ACCD9FA1AAA}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="10" totalsRowDxfId="8" dataCellStyle="Comma">
+    <tableColumn id="1" xr3:uid="{AF8A3B3E-9245-4703-A4D6-DA7EDF18BA10}" name="Model" totalsRowLabel="Mean" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{42978F44-899C-47DE-A9F1-9ACCD9FA1AAA}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Comma">
       <calculatedColumnFormula>B4*$B$1</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table1[Max Rate (Cases)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0C3F4248-BFB7-4BE6-94F1-FA698C4C1EBC}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="7">
+    <tableColumn id="3" xr3:uid="{0C3F4248-BFB7-4BE6-94F1-FA698C4C1EBC}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="18" totalsRowDxfId="17">
       <totalsRowFormula>AVERAGE(Table1[Half-Width (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EEA69209-B1F7-44C2-B9A1-9495B14A309C}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="6">
+    <tableColumn id="4" xr3:uid="{EEA69209-B1F7-44C2-B9A1-9495B14A309C}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="16" totalsRowDxfId="15">
       <totalsRowFormula>AVERAGE(Table1[Half-Width Adj (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{766EC484-E201-4982-B96C-9201B98C4515}" name="Max Week" totalsRowFunction="custom" dataDxfId="20" totalsRowDxfId="5">
+    <tableColumn id="5" xr3:uid="{766EC484-E201-4982-B96C-9201B98C4515}" name="Max Week" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="13">
       <totalsRowFormula>AVERAGE(Table1[Max Week])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -721,21 +1048,21 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8FB070A4-DEFC-4272-B34F-2AD810C2F9E2}" name="Table14" displayName="Table14" ref="I17:M28" totalsRowCount="1" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8FB070A4-DEFC-4272-B34F-2AD810C2F9E2}" name="Table14" displayName="Table14" ref="I17:M28" totalsRowCount="1" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="I17:M27" xr:uid="{8FB070A4-DEFC-4272-B34F-2AD810C2F9E2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C3A5743A-E35F-4AD8-974E-6A702D2AE592}" name="Model" totalsRowLabel="Mean" dataDxfId="17" totalsRowDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{DE8D9FF0-76B5-438F-A1DB-C2C2165BC8C0}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="16" totalsRowDxfId="3" dataCellStyle="Comma">
+    <tableColumn id="1" xr3:uid="{C3A5743A-E35F-4AD8-974E-6A702D2AE592}" name="Model" totalsRowLabel="Mean" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{DE8D9FF0-76B5-438F-A1DB-C2C2165BC8C0}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="8" totalsRowDxfId="7" dataCellStyle="Comma">
       <calculatedColumnFormula>B18*$B$1</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table14[Max Rate (Cases)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1F5586A0-CDE4-4A96-AB98-34EA914FEE01}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="2">
+    <tableColumn id="3" xr3:uid="{1F5586A0-CDE4-4A96-AB98-34EA914FEE01}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="5">
       <totalsRowFormula>AVERAGE(Table14[Half-Width (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{80B625EB-3697-4B57-ABB0-D47B504E2214}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="1">
+    <tableColumn id="4" xr3:uid="{80B625EB-3697-4B57-ABB0-D47B504E2214}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="3">
       <totalsRowFormula>AVERAGE(Table14[Half-Width Adj (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0264FFAF-4437-47B8-B04F-A28DE7E5145C}" name="Max Week" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="0">
+    <tableColumn id="5" xr3:uid="{0264FFAF-4437-47B8-B04F-A28DE7E5145C}" name="Max Week" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="1">
       <calculatedColumnFormula>D18+30</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table14[Max Week])</totalsRowFormula>
     </tableColumn>
@@ -1061,13 +1388,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B211DF-7FA1-4038-A4FC-A24EBE4CF847}">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="13" width="12.77734375" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" customWidth="1"/>
+    <col min="10" max="13" width="12.77734375" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" customWidth="1"/>
+    <col min="17" max="20" width="12.33203125" customWidth="1"/>
+    <col min="23" max="23" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1086,7 +1417,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1101,7 +1432,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1122,23 +1453,43 @@
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P3" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1178,8 +1529,39 @@
       <c r="M4" s="4">
         <v>51.546239</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="15">
+        <f>B4*$B$1</f>
+        <v>47528.734823999999</v>
+      </c>
+      <c r="R4" s="20">
+        <v>10.818647</v>
+      </c>
+      <c r="S4" s="20">
+        <v>5.2325020000000002</v>
+      </c>
+      <c r="T4" s="20">
+        <v>51.546239</v>
+      </c>
+      <c r="W4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" s="15">
+        <v>47528.734823999999</v>
+      </c>
+      <c r="Y4" s="20">
+        <v>10.818647</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>5.2325020000000002</v>
+      </c>
+      <c r="AA4" s="20">
+        <v>51.546239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1219,8 +1601,39 @@
       <c r="M5" s="4">
         <v>51.825242000000003</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="12">
+        <f t="shared" ref="Q5:Q13" si="2">B5*$B$1</f>
+        <v>38775.033719999999</v>
+      </c>
+      <c r="R5" s="21">
+        <v>11.514607</v>
+      </c>
+      <c r="S5" s="21">
+        <v>5.5691059999999997</v>
+      </c>
+      <c r="T5" s="21">
+        <v>51.825242000000003</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="12">
+        <v>38775.033719999999</v>
+      </c>
+      <c r="Y5" s="21">
+        <v>11.514607</v>
+      </c>
+      <c r="Z5" s="21">
+        <v>5.5691059999999997</v>
+      </c>
+      <c r="AA5" s="21">
+        <v>51.825242000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1260,8 +1673,39 @@
       <c r="M6" s="4">
         <v>50.648973999999995</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="12">
+        <f t="shared" si="2"/>
+        <v>43605.141407999996</v>
+      </c>
+      <c r="R6" s="21">
+        <v>9.4750730000000001</v>
+      </c>
+      <c r="S6" s="21">
+        <v>4.5826739999999999</v>
+      </c>
+      <c r="T6" s="21">
+        <v>50.648973999999995</v>
+      </c>
+      <c r="W6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="X6" s="12">
+        <v>43605.141407999996</v>
+      </c>
+      <c r="Y6" s="21">
+        <v>9.4750730000000001</v>
+      </c>
+      <c r="Z6" s="21">
+        <v>4.5826739999999999</v>
+      </c>
+      <c r="AA6" s="21">
+        <v>50.648973999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1745,39 @@
       <c r="M7" s="4">
         <v>52.646534000000003</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P7" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="12">
+        <f t="shared" si="2"/>
+        <v>42441.333264000001</v>
+      </c>
+      <c r="R7" s="21">
+        <v>8.7152670000000008</v>
+      </c>
+      <c r="S7" s="21">
+        <v>4.2151899999999998</v>
+      </c>
+      <c r="T7" s="21">
+        <v>52.646534000000003</v>
+      </c>
+      <c r="W7" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" s="12">
+        <v>42441.333264000001</v>
+      </c>
+      <c r="Y7" s="21">
+        <v>8.7152670000000008</v>
+      </c>
+      <c r="Z7" s="21">
+        <v>4.2151899999999998</v>
+      </c>
+      <c r="AA7" s="21">
+        <v>52.646534000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1817,39 @@
       <c r="M8" s="4">
         <v>51.607849999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="12">
+        <f t="shared" si="2"/>
+        <v>43653.625739999996</v>
+      </c>
+      <c r="R8" s="21">
+        <v>9.8766829999999999</v>
+      </c>
+      <c r="S8" s="21">
+        <v>4.7769149999999998</v>
+      </c>
+      <c r="T8" s="21">
+        <v>51.607849999999999</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="12">
+        <v>43653.625739999996</v>
+      </c>
+      <c r="Y8" s="21">
+        <v>9.8766829999999999</v>
+      </c>
+      <c r="Z8" s="21">
+        <v>4.7769149999999998</v>
+      </c>
+      <c r="AA8" s="21">
+        <v>51.607849999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1383,8 +1889,39 @@
       <c r="M9" s="4">
         <v>50.418517000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q9" s="12">
+        <f t="shared" si="2"/>
+        <v>53244.038412000002</v>
+      </c>
+      <c r="R9" s="21">
+        <v>11.655272999999999</v>
+      </c>
+      <c r="S9" s="21">
+        <v>5.6371399999999996</v>
+      </c>
+      <c r="T9" s="21">
+        <v>50.418517000000001</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="X9" s="12">
+        <v>53244.038412000002</v>
+      </c>
+      <c r="Y9" s="21">
+        <v>11.655272999999999</v>
+      </c>
+      <c r="Z9" s="21">
+        <v>5.6371399999999996</v>
+      </c>
+      <c r="AA9" s="21">
+        <v>50.418517000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -1424,8 +1961,39 @@
       <c r="M10" s="4">
         <v>51.911073000000002</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="12">
+        <f t="shared" si="2"/>
+        <v>37300.336488000001</v>
+      </c>
+      <c r="R10" s="21">
+        <v>9.9486910000000002</v>
+      </c>
+      <c r="S10" s="21">
+        <v>4.8117419999999997</v>
+      </c>
+      <c r="T10" s="21">
+        <v>51.911073000000002</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="X10" s="12">
+        <v>37300.336488000001</v>
+      </c>
+      <c r="Y10" s="21">
+        <v>9.9486910000000002</v>
+      </c>
+      <c r="Z10" s="21">
+        <v>4.8117419999999997</v>
+      </c>
+      <c r="AA10" s="21">
+        <v>51.911073000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1465,8 +2033,39 @@
       <c r="M11" s="4">
         <v>50.035004999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" s="12">
+        <f t="shared" si="2"/>
+        <v>41319.240984000004</v>
+      </c>
+      <c r="R11" s="21">
+        <v>11.50141</v>
+      </c>
+      <c r="S11" s="21">
+        <v>5.5627240000000002</v>
+      </c>
+      <c r="T11" s="21">
+        <v>50.035004999999998</v>
+      </c>
+      <c r="W11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="12">
+        <v>41319.240984000004</v>
+      </c>
+      <c r="Y11" s="21">
+        <v>11.50141</v>
+      </c>
+      <c r="Z11" s="21">
+        <v>5.5627240000000002</v>
+      </c>
+      <c r="AA11" s="21">
+        <v>50.035004999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -1506,8 +2105,39 @@
       <c r="M12" s="4">
         <v>50.718409000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="12">
+        <f t="shared" si="2"/>
+        <v>48984.185663999997</v>
+      </c>
+      <c r="R12" s="21">
+        <v>9.7740170000000006</v>
+      </c>
+      <c r="S12" s="21">
+        <v>4.7272600000000002</v>
+      </c>
+      <c r="T12" s="21">
+        <v>50.718409000000001</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12" s="12">
+        <v>48984.185663999997</v>
+      </c>
+      <c r="Y12" s="21">
+        <v>9.7740170000000006</v>
+      </c>
+      <c r="Z12" s="21">
+        <v>4.7272600000000002</v>
+      </c>
+      <c r="AA12" s="21">
+        <v>50.718409000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +2177,39 @@
       <c r="M13" s="4">
         <v>51.717542999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="17">
+        <f t="shared" si="2"/>
+        <v>44624.325347999998</v>
+      </c>
+      <c r="R13" s="22">
+        <v>8.7023620000000008</v>
+      </c>
+      <c r="S13" s="22">
+        <v>4.2089480000000004</v>
+      </c>
+      <c r="T13" s="22">
+        <v>51.717542999999999</v>
+      </c>
+      <c r="W13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="X13" s="12">
+        <v>44624.325347999998</v>
+      </c>
+      <c r="Y13" s="21">
+        <v>8.7023620000000008</v>
+      </c>
+      <c r="Z13" s="21">
+        <v>4.2089480000000004</v>
+      </c>
+      <c r="AA13" s="21">
+        <v>51.717542999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="I14" s="3" t="s">
         <v>30</v>
       </c>
@@ -1568,8 +2229,32 @@
         <f>AVERAGE(Table1[Max Week])</f>
         <v>51.307538600000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="26">
+        <f>AVERAGE(Q4:Q13)</f>
+        <v>44147.599585199991</v>
+      </c>
+      <c r="R14" s="27">
+        <f t="shared" ref="R14:T14" si="3">AVERAGE(R4:R13)</f>
+        <v>10.198203000000001</v>
+      </c>
+      <c r="S14" s="27">
+        <f t="shared" si="3"/>
+        <v>4.9324200999999999</v>
+      </c>
+      <c r="T14" s="28">
+        <f t="shared" si="3"/>
+        <v>51.307538600000001</v>
+      </c>
+      <c r="W14" s="18"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="28"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="I15" t="s">
         <v>31</v>
       </c>
@@ -1589,8 +2274,44 @@
         <f>STDEV(Table1[Max Week])</f>
         <v>0.81178335067446938</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="P15" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="19">
+        <f>STDEV(Q4:Q13)</f>
+        <v>4772.5582616910733</v>
+      </c>
+      <c r="R15" s="24">
+        <f t="shared" ref="R15:T15" si="4">STDEV(R4:R13)</f>
+        <v>1.1177553550416162</v>
+      </c>
+      <c r="S15" s="24">
+        <f t="shared" si="4"/>
+        <v>0.54060872713028429</v>
+      </c>
+      <c r="T15" s="23">
+        <f t="shared" si="4"/>
+        <v>0.81178335067446938</v>
+      </c>
+      <c r="W15" s="18"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="23"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1621,8 +2342,28 @@
       <c r="M17" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="R17" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="S17" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1658,8 +2399,29 @@
         <f>D18+30</f>
         <v>52.329311000000004</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="15">
+        <f>B18*$B$1</f>
+        <v>45246.886272000003</v>
+      </c>
+      <c r="R18" s="20">
+        <v>4.9343019999999997</v>
+      </c>
+      <c r="S18" s="20">
+        <v>3.924741</v>
+      </c>
+      <c r="T18" s="20">
+        <v>52.329311000000004</v>
+      </c>
+      <c r="W18" s="14"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +2444,7 @@
         <v>23</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" ref="J19:J27" si="2">B19*$B$1</f>
+        <f t="shared" ref="J19:J27" si="5">B19*$B$1</f>
         <v>63308.796371999997</v>
       </c>
       <c r="K19" s="1">
@@ -1692,11 +2454,32 @@
         <v>5.6328120000000004</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" ref="M19:M27" si="3">D19+30</f>
+        <f t="shared" ref="M19:M27" si="6">D19+30</f>
         <v>52.030391999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P19" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q19" s="12">
+        <f t="shared" ref="Q19:Q27" si="7">B19*$B$1</f>
+        <v>63308.796371999997</v>
+      </c>
+      <c r="R19" s="21">
+        <v>7.0817410000000001</v>
+      </c>
+      <c r="S19" s="21">
+        <v>5.6328120000000004</v>
+      </c>
+      <c r="T19" s="21">
+        <v>52.030391999999999</v>
+      </c>
+      <c r="W19" s="13"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1719,7 +2502,7 @@
         <v>22</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>65972.027375999998</v>
       </c>
       <c r="K20" s="1">
@@ -1729,11 +2512,32 @@
         <v>4.0929089999999997</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>50.619607999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P20" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q20" s="12">
+        <f t="shared" si="7"/>
+        <v>65972.027375999998</v>
+      </c>
+      <c r="R20" s="21">
+        <v>5.1457280000000001</v>
+      </c>
+      <c r="S20" s="21">
+        <v>4.0929089999999997</v>
+      </c>
+      <c r="T20" s="21">
+        <v>50.619607999999999</v>
+      </c>
+      <c r="W20" s="13"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="21"/>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1756,7 +2560,7 @@
         <v>24</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>69146.530956000002</v>
       </c>
       <c r="K21" s="1">
@@ -1766,11 +2570,32 @@
         <v>5.7762979999999997</v>
       </c>
       <c r="M21" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>52.438113999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P21" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q21" s="12">
+        <f t="shared" si="7"/>
+        <v>69146.530956000002</v>
+      </c>
+      <c r="R21" s="21">
+        <v>7.2621359999999999</v>
+      </c>
+      <c r="S21" s="21">
+        <v>5.7762979999999997</v>
+      </c>
+      <c r="T21" s="21">
+        <v>52.438113999999999</v>
+      </c>
+      <c r="W21" s="13"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="21"/>
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="21"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1793,7 +2618,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>54732.042359999999</v>
       </c>
       <c r="K22" s="1">
@@ -1803,11 +2628,32 @@
         <v>5.5572900000000001</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>52.524986999999996</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P22" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" s="12">
+        <f t="shared" si="7"/>
+        <v>54732.042359999999</v>
+      </c>
+      <c r="R22" s="21">
+        <v>6.9867920000000003</v>
+      </c>
+      <c r="S22" s="21">
+        <v>5.5572900000000001</v>
+      </c>
+      <c r="T22" s="21">
+        <v>52.524986999999996</v>
+      </c>
+      <c r="W22" s="13"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1830,7 +2676,7 @@
         <v>21</v>
       </c>
       <c r="J23" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>84867.978492000009</v>
       </c>
       <c r="K23" s="1">
@@ -1840,11 +2686,32 @@
         <v>4.8393110000000004</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>50.507648000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="12">
+        <f t="shared" si="7"/>
+        <v>84867.978492000009</v>
+      </c>
+      <c r="R23" s="21">
+        <v>6.0841279999999998</v>
+      </c>
+      <c r="S23" s="21">
+        <v>4.8393110000000004</v>
+      </c>
+      <c r="T23" s="21">
+        <v>50.507648000000003</v>
+      </c>
+      <c r="W23" s="13"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1867,7 +2734,7 @@
         <v>25</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>65459.373480000002</v>
       </c>
       <c r="K24" s="1">
@@ -1877,11 +2744,32 @@
         <v>6.2979329999999996</v>
       </c>
       <c r="M24" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>51.984837999999996</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P24" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q24" s="12">
+        <f t="shared" si="7"/>
+        <v>65459.373480000002</v>
+      </c>
+      <c r="R24" s="21">
+        <v>7.9179510000000004</v>
+      </c>
+      <c r="S24" s="21">
+        <v>6.2979329999999996</v>
+      </c>
+      <c r="T24" s="21">
+        <v>51.984837999999996</v>
+      </c>
+      <c r="W24" s="13"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="21"/>
+      <c r="Z24" s="21"/>
+      <c r="AA24" s="21"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1904,7 +2792,7 @@
         <v>26</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>71774.169947999995</v>
       </c>
       <c r="K25" s="1">
@@ -1914,11 +2802,32 @@
         <v>4.3599129999999997</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>51.186745000000002</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q25" s="12">
+        <f t="shared" si="7"/>
+        <v>71774.169947999995</v>
+      </c>
+      <c r="R25" s="21">
+        <v>5.481414</v>
+      </c>
+      <c r="S25" s="21">
+        <v>4.3599129999999997</v>
+      </c>
+      <c r="T25" s="21">
+        <v>51.186745000000002</v>
+      </c>
+      <c r="W25" s="13"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1941,7 +2850,7 @@
         <v>27</v>
       </c>
       <c r="J26" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>67514.409287999995</v>
       </c>
       <c r="K26" s="1">
@@ -1951,11 +2860,32 @@
         <v>5.3575520000000001</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>51.122333999999995</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P26" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q26" s="12">
+        <f t="shared" si="7"/>
+        <v>67514.409287999995</v>
+      </c>
+      <c r="R26" s="21">
+        <v>6.7356749999999996</v>
+      </c>
+      <c r="S26" s="21">
+        <v>5.3575520000000001</v>
+      </c>
+      <c r="T26" s="21">
+        <v>51.122333999999995</v>
+      </c>
+      <c r="W26" s="13"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+    </row>
+    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -1978,7 +2908,7 @@
         <v>28</v>
       </c>
       <c r="J27" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>69237.559943999993</v>
       </c>
       <c r="K27" s="1">
@@ -1988,11 +2918,32 @@
         <v>5.6045119999999997</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>51.900856000000005</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P27" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q27" s="17">
+        <f t="shared" si="7"/>
+        <v>69237.559943999993</v>
+      </c>
+      <c r="R27" s="22">
+        <v>7.0461600000000004</v>
+      </c>
+      <c r="S27" s="22">
+        <v>5.6045119999999997</v>
+      </c>
+      <c r="T27" s="22">
+        <v>51.900856000000005</v>
+      </c>
+      <c r="W27" s="16"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="I28" s="3" t="s">
         <v>30</v>
       </c>
@@ -2012,8 +2963,32 @@
         <f>AVERAGE(Table14[Max Week])</f>
         <v>51.664483299999993</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P28" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q28" s="26">
+        <f>AVERAGE(Q18:Q27)</f>
+        <v>65725.977448799997</v>
+      </c>
+      <c r="R28" s="27">
+        <f t="shared" ref="R28" si="8">AVERAGE(R18:R27)</f>
+        <v>6.4676027000000005</v>
+      </c>
+      <c r="S28" s="27">
+        <f t="shared" ref="S28" si="9">AVERAGE(S18:S27)</f>
+        <v>5.1443270999999999</v>
+      </c>
+      <c r="T28" s="28">
+        <f t="shared" ref="T28" si="10">AVERAGE(T18:T27)</f>
+        <v>51.664483299999993</v>
+      </c>
+      <c r="W28" s="18"/>
+      <c r="X28" s="26"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="28"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="I29" t="s">
         <v>31</v>
       </c>
@@ -2033,8 +3008,376 @@
         <f>STDEV(Table14[Max Week])</f>
         <v>0.7472577543473421</v>
       </c>
+      <c r="P29" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q29" s="19">
+        <f>STDEV(Q18:Q27)</f>
+        <v>10416.124730277312</v>
+      </c>
+      <c r="R29" s="24">
+        <f t="shared" ref="R29:T29" si="11">STDEV(R18:R27)</f>
+        <v>1.0003384316743371</v>
+      </c>
+      <c r="S29" s="24">
+        <f t="shared" si="11"/>
+        <v>0.7956684976443722</v>
+      </c>
+      <c r="T29" s="23">
+        <f t="shared" si="11"/>
+        <v>0.7472577543473421</v>
+      </c>
+      <c r="W29" s="18"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="24"/>
+      <c r="Z29" s="24"/>
+      <c r="AA29" s="23"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="29">
+        <v>0.83205119999999999</v>
+      </c>
+      <c r="C32">
+        <v>5.6545860000000001</v>
+      </c>
+      <c r="D32">
+        <v>13.658386999999999</v>
+      </c>
+      <c r="E32" s="29">
+        <v>-2.3639699999999999E-17</v>
+      </c>
+      <c r="F32">
+        <v>19.669132000000001</v>
+      </c>
+      <c r="G32">
+        <v>25.252524999999999</v>
+      </c>
+      <c r="H32">
+        <v>3.6482000000000001E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="29">
+        <v>0.79006240000000005</v>
+      </c>
+      <c r="C33">
+        <v>3.7615189999999998</v>
+      </c>
+      <c r="D33">
+        <v>17.031714000000001</v>
+      </c>
+      <c r="E33" s="29">
+        <v>0.31906299999999999</v>
+      </c>
+      <c r="F33">
+        <v>10.349474000000001</v>
+      </c>
+      <c r="G33">
+        <v>24.317537999999999</v>
+      </c>
+      <c r="H33">
+        <v>1.9481999999999999E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="J34" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="34"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="J35" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I36" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J36" s="35">
+        <f>B32*$B$1</f>
+        <v>38310.965452800003</v>
+      </c>
+      <c r="K36" s="35">
+        <f>B33*$B$1</f>
+        <v>36377.633145600004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I37" t="s">
+        <v>54</v>
+      </c>
+      <c r="J37" s="33">
+        <f>D32+35</f>
+        <v>48.658386999999998</v>
+      </c>
+      <c r="K37" s="33">
+        <f>D33+35</f>
+        <v>52.031714000000001</v>
+      </c>
+      <c r="P37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I38" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38" s="33">
+        <v>5.6545860000000001</v>
+      </c>
+      <c r="K38" s="33">
+        <v>3.7615189999999998</v>
+      </c>
+      <c r="P38" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38" s="12">
+        <v>47528.734823999999</v>
+      </c>
+      <c r="R38" s="21">
+        <v>10.818647</v>
+      </c>
+      <c r="S38" s="21">
+        <v>5.2325020000000002</v>
+      </c>
+      <c r="T38" s="21">
+        <v>51.546239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I39" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J39" s="10">
+        <f>-2.36397E-17*B1</f>
+        <v>-1.0884663467999999E-12</v>
+      </c>
+      <c r="K39" s="10">
+        <f>0.319063*B1</f>
+        <v>14690.936771999999</v>
+      </c>
+      <c r="P39" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q39" s="12">
+        <v>38775.033719999999</v>
+      </c>
+      <c r="R39" s="21">
+        <v>11.514607</v>
+      </c>
+      <c r="S39" s="21">
+        <v>5.5691059999999997</v>
+      </c>
+      <c r="T39" s="21">
+        <v>51.825242000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I40" t="s">
+        <v>57</v>
+      </c>
+      <c r="J40" s="33">
+        <f>G32+35 - 52</f>
+        <v>8.2525249999999986</v>
+      </c>
+      <c r="K40" s="33">
+        <f>G33+35-52</f>
+        <v>7.317537999999999</v>
+      </c>
+      <c r="P40" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="12">
+        <v>43605.141407999996</v>
+      </c>
+      <c r="R40" s="21">
+        <v>9.4750730000000001</v>
+      </c>
+      <c r="S40" s="21">
+        <v>4.5826739999999999</v>
+      </c>
+      <c r="T40" s="21">
+        <v>50.648973999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I41" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="J41" s="33">
+        <v>19.669132000000001</v>
+      </c>
+      <c r="K41" s="33">
+        <v>10.349474000000001</v>
+      </c>
+      <c r="P41" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q41" s="12">
+        <v>42441.333264000001</v>
+      </c>
+      <c r="R41" s="21">
+        <v>8.7152670000000008</v>
+      </c>
+      <c r="S41" s="21">
+        <v>4.2151899999999998</v>
+      </c>
+      <c r="T41" s="21">
+        <v>52.646534000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="I42" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J42" s="32">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="K42" s="32">
+        <v>1.26</v>
+      </c>
+      <c r="P42" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q42" s="12">
+        <v>43653.625739999996</v>
+      </c>
+      <c r="R42" s="21">
+        <v>9.8766829999999999</v>
+      </c>
+      <c r="S42" s="21">
+        <v>4.7769149999999998</v>
+      </c>
+      <c r="T42" s="21">
+        <v>51.607849999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P43" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q43" s="12">
+        <v>53244.038412000002</v>
+      </c>
+      <c r="R43" s="21">
+        <v>11.655272999999999</v>
+      </c>
+      <c r="S43" s="21">
+        <v>5.6371399999999996</v>
+      </c>
+      <c r="T43" s="21">
+        <v>50.418517000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P44" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q44" s="12">
+        <v>37300.336488000001</v>
+      </c>
+      <c r="R44" s="21">
+        <v>9.9486910000000002</v>
+      </c>
+      <c r="S44" s="21">
+        <v>4.8117419999999997</v>
+      </c>
+      <c r="T44" s="21">
+        <v>51.911073000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P45" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q45" s="12">
+        <v>41319.240984000004</v>
+      </c>
+      <c r="R45" s="21">
+        <v>11.50141</v>
+      </c>
+      <c r="S45" s="21">
+        <v>5.5627240000000002</v>
+      </c>
+      <c r="T45" s="21">
+        <v>50.035004999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P46" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q46" s="12">
+        <v>48984.185663999997</v>
+      </c>
+      <c r="R46" s="21">
+        <v>9.7740170000000006</v>
+      </c>
+      <c r="S46" s="21">
+        <v>4.7272600000000002</v>
+      </c>
+      <c r="T46" s="21">
+        <v>50.718409000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P47" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q47" s="12">
+        <v>44624.325347999998</v>
+      </c>
+      <c r="R47" s="21">
+        <v>8.7023620000000008</v>
+      </c>
+      <c r="S47" s="21">
+        <v>4.2089480000000004</v>
+      </c>
+      <c r="T47" s="21">
+        <v>51.717542999999999</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J34:K34"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>

--- a/data/FluTables.xlsx
+++ b/data/FluTables.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christopher.johnson\Documents\GitHub\flu\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28A349-6DB4-436E-8CBE-DFE992169005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3B5B24-6865-4315-A18D-82F270A7E744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2460" windowWidth="29040" windowHeight="15840" xr2:uid="{11A36013-8756-48B6-B10C-B88575A86A49}"/>
+    <workbookView xWindow="-28920" yWindow="-1785" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{11A36013-8756-48B6-B10C-B88575A86A49}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="73">
   <si>
     <t>Max</t>
   </si>
@@ -317,6 +319,45 @@
       <t>adj</t>
     </r>
   </si>
+  <si>
+    <t>09-10</t>
+  </si>
+  <si>
+    <t>10-11</t>
+  </si>
+  <si>
+    <t>11-12</t>
+  </si>
+  <si>
+    <t>12-13</t>
+  </si>
+  <si>
+    <t>13-14</t>
+  </si>
+  <si>
+    <t>14-15</t>
+  </si>
+  <si>
+    <t>15-16</t>
+  </si>
+  <si>
+    <t>16-17</t>
+  </si>
+  <si>
+    <t>17-18</t>
+  </si>
+  <si>
+    <t>18-19</t>
+  </si>
+  <si>
+    <t>19-20</t>
+  </si>
+  <si>
+    <t>21-22</t>
+  </si>
+  <si>
+    <t>24-25</t>
+  </si>
 </sst>
 </file>
 
@@ -326,9 +367,9 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,6 +447,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -446,7 +493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -468,13 +515,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -489,49 +533,48 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -539,31 +582,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1011,6 +1029,31 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1025,21 +1068,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F15C92B-7033-4A99-B09C-6CF49AEAF9BE}" name="Table1" displayName="Table1" ref="I3:M14" totalsRowCount="1" headerRowDxfId="0" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F15C92B-7033-4A99-B09C-6CF49AEAF9BE}" name="Table1" displayName="Table1" ref="I3:M14" totalsRowCount="1" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="I3:M13" xr:uid="{5F15C92B-7033-4A99-B09C-6CF49AEAF9BE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AF8A3B3E-9245-4703-A4D6-DA7EDF18BA10}" name="Model" totalsRowLabel="Mean" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{42978F44-899C-47DE-A9F1-9ACCD9FA1AAA}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Comma">
+    <tableColumn id="1" xr3:uid="{AF8A3B3E-9245-4703-A4D6-DA7EDF18BA10}" name="Model" totalsRowLabel="Mean" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{42978F44-899C-47DE-A9F1-9ACCD9FA1AAA}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Comma">
       <calculatedColumnFormula>B4*$B$1</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table1[Max Rate (Cases)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0C3F4248-BFB7-4BE6-94F1-FA698C4C1EBC}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="18" totalsRowDxfId="17">
+    <tableColumn id="3" xr3:uid="{0C3F4248-BFB7-4BE6-94F1-FA698C4C1EBC}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
       <totalsRowFormula>AVERAGE(Table1[Half-Width (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EEA69209-B1F7-44C2-B9A1-9495B14A309C}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="16" totalsRowDxfId="15">
+    <tableColumn id="4" xr3:uid="{EEA69209-B1F7-44C2-B9A1-9495B14A309C}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
       <totalsRowFormula>AVERAGE(Table1[Half-Width Adj (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{766EC484-E201-4982-B96C-9201B98C4515}" name="Max Week" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="13">
+    <tableColumn id="5" xr3:uid="{766EC484-E201-4982-B96C-9201B98C4515}" name="Max Week" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
       <totalsRowFormula>AVERAGE(Table1[Max Week])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -1048,21 +1091,21 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8FB070A4-DEFC-4272-B34F-2AD810C2F9E2}" name="Table14" displayName="Table14" ref="I17:M28" totalsRowCount="1" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8FB070A4-DEFC-4272-B34F-2AD810C2F9E2}" name="Table14" displayName="Table14" ref="I17:M28" totalsRowCount="1" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="I17:M27" xr:uid="{8FB070A4-DEFC-4272-B34F-2AD810C2F9E2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C3A5743A-E35F-4AD8-974E-6A702D2AE592}" name="Model" totalsRowLabel="Mean" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{DE8D9FF0-76B5-438F-A1DB-C2C2165BC8C0}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="8" totalsRowDxfId="7" dataCellStyle="Comma">
+    <tableColumn id="1" xr3:uid="{C3A5743A-E35F-4AD8-974E-6A702D2AE592}" name="Model" totalsRowLabel="Mean" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{DE8D9FF0-76B5-438F-A1DB-C2C2165BC8C0}" name="Max Rate (Cases)" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Comma">
       <calculatedColumnFormula>B18*$B$1</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table14[Max Rate (Cases)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1F5586A0-CDE4-4A96-AB98-34EA914FEE01}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="3" xr3:uid="{1F5586A0-CDE4-4A96-AB98-34EA914FEE01}" name="Half-Width (Weeks)" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
       <totalsRowFormula>AVERAGE(Table14[Half-Width (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{80B625EB-3697-4B57-ABB0-D47B504E2214}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="3">
+    <tableColumn id="4" xr3:uid="{80B625EB-3697-4B57-ABB0-D47B504E2214}" name="Half-Width Adj (Weeks)" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
       <totalsRowFormula>AVERAGE(Table14[Half-Width Adj (Weeks)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0264FFAF-4437-47B8-B04F-A28DE7E5145C}" name="Max Week" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="1">
+    <tableColumn id="5" xr3:uid="{0264FFAF-4437-47B8-B04F-A28DE7E5145C}" name="Max Week" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>D18+30</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table14[Max Week])</totalsRowFormula>
     </tableColumn>
@@ -1389,21 +1432,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B211DF-7FA1-4038-A4FC-A24EBE4CF847}">
   <dimension ref="A1:AA47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="5.77734375" customWidth="1"/>
-    <col min="10" max="13" width="12.77734375" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" customWidth="1"/>
-    <col min="17" max="20" width="12.33203125" customWidth="1"/>
-    <col min="23" max="23" width="12.77734375" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="13" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="17" max="20" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46044</v>
+        <v>32767</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -1417,7 +1460,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1432,7 +1475,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1453,43 +1496,43 @@
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="R3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="T3" s="25" t="s">
+      <c r="T3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1518,7 +1561,7 @@
       </c>
       <c r="J4" s="5">
         <f>B4*$B$1</f>
-        <v>47528.734823999999</v>
+        <v>33823.604681999997</v>
       </c>
       <c r="K4" s="6">
         <v>10.818647</v>
@@ -1529,39 +1572,39 @@
       <c r="M4" s="4">
         <v>51.546239</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="14">
         <f>B4*$B$1</f>
+        <v>33823.604681999997</v>
+      </c>
+      <c r="R4" s="19">
+        <v>10.818647</v>
+      </c>
+      <c r="S4" s="19">
+        <v>5.2325020000000002</v>
+      </c>
+      <c r="T4" s="19">
+        <v>51.546239</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" s="14">
         <v>47528.734823999999</v>
       </c>
-      <c r="R4" s="20">
+      <c r="Y4" s="19">
         <v>10.818647</v>
       </c>
-      <c r="S4" s="20">
+      <c r="Z4" s="19">
         <v>5.2325020000000002</v>
       </c>
-      <c r="T4" s="20">
+      <c r="AA4" s="19">
         <v>51.546239</v>
       </c>
-      <c r="W4" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" s="15">
-        <v>47528.734823999999</v>
-      </c>
-      <c r="Y4" s="20">
-        <v>10.818647</v>
-      </c>
-      <c r="Z4" s="20">
-        <v>5.2325020000000002</v>
-      </c>
-      <c r="AA4" s="20">
-        <v>51.546239</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1590,7 +1633,7 @@
       </c>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J13" si="1">B5*$B$1</f>
-        <v>38775.033719999999</v>
+        <v>27594.073710000001</v>
       </c>
       <c r="K5" s="6">
         <v>11.514607</v>
@@ -1601,39 +1644,39 @@
       <c r="M5" s="4">
         <v>51.825242000000003</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="11">
         <f t="shared" ref="Q5:Q13" si="2">B5*$B$1</f>
+        <v>27594.073710000001</v>
+      </c>
+      <c r="R5" s="20">
+        <v>11.514607</v>
+      </c>
+      <c r="S5" s="20">
+        <v>5.5691059999999997</v>
+      </c>
+      <c r="T5" s="20">
+        <v>51.825242000000003</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="11">
         <v>38775.033719999999</v>
       </c>
-      <c r="R5" s="21">
+      <c r="Y5" s="20">
         <v>11.514607</v>
       </c>
-      <c r="S5" s="21">
+      <c r="Z5" s="20">
         <v>5.5691059999999997</v>
       </c>
-      <c r="T5" s="21">
+      <c r="AA5" s="20">
         <v>51.825242000000003</v>
       </c>
-      <c r="W5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="X5" s="12">
-        <v>38775.033719999999</v>
-      </c>
-      <c r="Y5" s="21">
-        <v>11.514607</v>
-      </c>
-      <c r="Z5" s="21">
-        <v>5.5691059999999997</v>
-      </c>
-      <c r="AA5" s="21">
-        <v>51.825242000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1662,7 +1705,7 @@
       </c>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>43605.141407999996</v>
+        <v>31031.397543999999</v>
       </c>
       <c r="K6" s="6">
         <v>9.4750730000000001</v>
@@ -1673,39 +1716,39 @@
       <c r="M6" s="4">
         <v>50.648973999999995</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="11">
         <f t="shared" si="2"/>
+        <v>31031.397543999999</v>
+      </c>
+      <c r="R6" s="20">
+        <v>9.4750730000000001</v>
+      </c>
+      <c r="S6" s="20">
+        <v>4.5826739999999999</v>
+      </c>
+      <c r="T6" s="20">
+        <v>50.648973999999995</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="X6" s="11">
         <v>43605.141407999996</v>
       </c>
-      <c r="R6" s="21">
+      <c r="Y6" s="20">
         <v>9.4750730000000001</v>
       </c>
-      <c r="S6" s="21">
+      <c r="Z6" s="20">
         <v>4.5826739999999999</v>
       </c>
-      <c r="T6" s="21">
+      <c r="AA6" s="20">
         <v>50.648973999999995</v>
       </c>
-      <c r="W6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="X6" s="12">
-        <v>43605.141407999996</v>
-      </c>
-      <c r="Y6" s="21">
-        <v>9.4750730000000001</v>
-      </c>
-      <c r="Z6" s="21">
-        <v>4.5826739999999999</v>
-      </c>
-      <c r="AA6" s="21">
-        <v>50.648973999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -1734,7 +1777,7 @@
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>42441.333264000001</v>
+        <v>30203.178852000001</v>
       </c>
       <c r="K7" s="6">
         <v>8.7152670000000008</v>
@@ -1745,39 +1788,39 @@
       <c r="M7" s="4">
         <v>52.646534000000003</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="P7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="11">
         <f t="shared" si="2"/>
+        <v>30203.178852000001</v>
+      </c>
+      <c r="R7" s="20">
+        <v>8.7152670000000008</v>
+      </c>
+      <c r="S7" s="20">
+        <v>4.2151899999999998</v>
+      </c>
+      <c r="T7" s="20">
+        <v>52.646534000000003</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" s="11">
         <v>42441.333264000001</v>
       </c>
-      <c r="R7" s="21">
+      <c r="Y7" s="20">
         <v>8.7152670000000008</v>
       </c>
-      <c r="S7" s="21">
+      <c r="Z7" s="20">
         <v>4.2151899999999998</v>
       </c>
-      <c r="T7" s="21">
+      <c r="AA7" s="20">
         <v>52.646534000000003</v>
       </c>
-      <c r="W7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X7" s="12">
-        <v>42441.333264000001</v>
-      </c>
-      <c r="Y7" s="21">
-        <v>8.7152670000000008</v>
-      </c>
-      <c r="Z7" s="21">
-        <v>4.2151899999999998</v>
-      </c>
-      <c r="AA7" s="21">
-        <v>52.646534000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1806,7 +1849,7 @@
       </c>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>43653.625739999996</v>
+        <v>31065.901194999999</v>
       </c>
       <c r="K8" s="6">
         <v>9.8766829999999999</v>
@@ -1817,39 +1860,39 @@
       <c r="M8" s="4">
         <v>51.607849999999999</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="P8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="11">
         <f t="shared" si="2"/>
+        <v>31065.901194999999</v>
+      </c>
+      <c r="R8" s="20">
+        <v>9.8766829999999999</v>
+      </c>
+      <c r="S8" s="20">
+        <v>4.7769149999999998</v>
+      </c>
+      <c r="T8" s="20">
+        <v>51.607849999999999</v>
+      </c>
+      <c r="W8" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" s="11">
         <v>43653.625739999996</v>
       </c>
-      <c r="R8" s="21">
+      <c r="Y8" s="20">
         <v>9.8766829999999999</v>
       </c>
-      <c r="S8" s="21">
+      <c r="Z8" s="20">
         <v>4.7769149999999998</v>
       </c>
-      <c r="T8" s="21">
+      <c r="AA8" s="20">
         <v>51.607849999999999</v>
       </c>
-      <c r="W8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="X8" s="12">
-        <v>43653.625739999996</v>
-      </c>
-      <c r="Y8" s="21">
-        <v>9.8766829999999999</v>
-      </c>
-      <c r="Z8" s="21">
-        <v>4.7769149999999998</v>
-      </c>
-      <c r="AA8" s="21">
-        <v>51.607849999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1878,7 +1921,7 @@
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>53244.038412000002</v>
+        <v>37890.874091000005</v>
       </c>
       <c r="K9" s="6">
         <v>11.655272999999999</v>
@@ -1889,39 +1932,39 @@
       <c r="M9" s="4">
         <v>50.418517000000001</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="P9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="11">
         <f t="shared" si="2"/>
+        <v>37890.874091000005</v>
+      </c>
+      <c r="R9" s="20">
+        <v>11.655272999999999</v>
+      </c>
+      <c r="S9" s="20">
+        <v>5.6371399999999996</v>
+      </c>
+      <c r="T9" s="20">
+        <v>50.418517000000001</v>
+      </c>
+      <c r="W9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="X9" s="11">
         <v>53244.038412000002</v>
       </c>
-      <c r="R9" s="21">
+      <c r="Y9" s="20">
         <v>11.655272999999999</v>
       </c>
-      <c r="S9" s="21">
+      <c r="Z9" s="20">
         <v>5.6371399999999996</v>
       </c>
-      <c r="T9" s="21">
+      <c r="AA9" s="20">
         <v>50.418517000000001</v>
       </c>
-      <c r="W9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="X9" s="12">
-        <v>53244.038412000002</v>
-      </c>
-      <c r="Y9" s="21">
-        <v>11.655272999999999</v>
-      </c>
-      <c r="Z9" s="21">
-        <v>5.6371399999999996</v>
-      </c>
-      <c r="AA9" s="21">
-        <v>50.418517000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -1950,7 +1993,7 @@
       </c>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>37300.336488000001</v>
+        <v>26544.612234</v>
       </c>
       <c r="K10" s="6">
         <v>9.9486910000000002</v>
@@ -1961,39 +2004,39 @@
       <c r="M10" s="4">
         <v>51.911073000000002</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="P10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="11">
         <f t="shared" si="2"/>
+        <v>26544.612234</v>
+      </c>
+      <c r="R10" s="20">
+        <v>9.9486910000000002</v>
+      </c>
+      <c r="S10" s="20">
+        <v>4.8117419999999997</v>
+      </c>
+      <c r="T10" s="20">
+        <v>51.911073000000002</v>
+      </c>
+      <c r="W10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="X10" s="11">
         <v>37300.336488000001</v>
       </c>
-      <c r="R10" s="21">
+      <c r="Y10" s="20">
         <v>9.9486910000000002</v>
       </c>
-      <c r="S10" s="21">
+      <c r="Z10" s="20">
         <v>4.8117419999999997</v>
       </c>
-      <c r="T10" s="21">
+      <c r="AA10" s="20">
         <v>51.911073000000002</v>
       </c>
-      <c r="W10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="X10" s="12">
-        <v>37300.336488000001</v>
-      </c>
-      <c r="Y10" s="21">
-        <v>9.9486910000000002</v>
-      </c>
-      <c r="Z10" s="21">
-        <v>4.8117419999999997</v>
-      </c>
-      <c r="AA10" s="21">
-        <v>51.911073000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -2022,7 +2065,7 @@
       </c>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>41319.240984000004</v>
+        <v>29404.647062</v>
       </c>
       <c r="K11" s="6">
         <v>11.50141</v>
@@ -2033,39 +2076,39 @@
       <c r="M11" s="4">
         <v>50.035004999999998</v>
       </c>
-      <c r="P11" s="13" t="s">
+      <c r="P11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="11">
         <f t="shared" si="2"/>
+        <v>29404.647062</v>
+      </c>
+      <c r="R11" s="20">
+        <v>11.50141</v>
+      </c>
+      <c r="S11" s="20">
+        <v>5.5627240000000002</v>
+      </c>
+      <c r="T11" s="20">
+        <v>50.035004999999998</v>
+      </c>
+      <c r="W11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="11">
         <v>41319.240984000004</v>
       </c>
-      <c r="R11" s="21">
+      <c r="Y11" s="20">
         <v>11.50141</v>
       </c>
-      <c r="S11" s="21">
+      <c r="Z11" s="20">
         <v>5.5627240000000002</v>
       </c>
-      <c r="T11" s="21">
+      <c r="AA11" s="20">
         <v>50.035004999999998</v>
       </c>
-      <c r="W11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="X11" s="12">
-        <v>41319.240984000004</v>
-      </c>
-      <c r="Y11" s="21">
-        <v>11.50141</v>
-      </c>
-      <c r="Z11" s="21">
-        <v>5.5627240000000002</v>
-      </c>
-      <c r="AA11" s="21">
-        <v>50.035004999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -2094,7 +2137,7 @@
       </c>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>48984.185663999997</v>
+        <v>34859.369551999996</v>
       </c>
       <c r="K12" s="6">
         <v>9.7740170000000006</v>
@@ -2105,39 +2148,39 @@
       <c r="M12" s="4">
         <v>50.718409000000001</v>
       </c>
-      <c r="P12" s="13" t="s">
+      <c r="P12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="11">
         <f t="shared" si="2"/>
+        <v>34859.369551999996</v>
+      </c>
+      <c r="R12" s="20">
+        <v>9.7740170000000006</v>
+      </c>
+      <c r="S12" s="20">
+        <v>4.7272600000000002</v>
+      </c>
+      <c r="T12" s="20">
+        <v>50.718409000000001</v>
+      </c>
+      <c r="W12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12" s="11">
         <v>48984.185663999997</v>
       </c>
-      <c r="R12" s="21">
+      <c r="Y12" s="20">
         <v>9.7740170000000006</v>
       </c>
-      <c r="S12" s="21">
+      <c r="Z12" s="20">
         <v>4.7272600000000002</v>
       </c>
-      <c r="T12" s="21">
+      <c r="AA12" s="20">
         <v>50.718409000000001</v>
       </c>
-      <c r="W12" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="X12" s="12">
-        <v>48984.185663999997</v>
-      </c>
-      <c r="Y12" s="21">
-        <v>9.7740170000000006</v>
-      </c>
-      <c r="Z12" s="21">
-        <v>4.7272600000000002</v>
-      </c>
-      <c r="AA12" s="21">
-        <v>50.718409000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
@@ -2166,7 +2209,7 @@
       </c>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>44624.325347999998</v>
+        <v>31756.695089000001</v>
       </c>
       <c r="K13" s="6">
         <v>8.7023620000000008</v>
@@ -2177,45 +2220,45 @@
       <c r="M13" s="4">
         <v>51.717542999999999</v>
       </c>
-      <c r="P13" s="16" t="s">
+      <c r="P13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="16">
         <f t="shared" si="2"/>
+        <v>31756.695089000001</v>
+      </c>
+      <c r="R13" s="21">
+        <v>8.7023620000000008</v>
+      </c>
+      <c r="S13" s="21">
+        <v>4.2089480000000004</v>
+      </c>
+      <c r="T13" s="21">
+        <v>51.717542999999999</v>
+      </c>
+      <c r="W13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="X13" s="11">
         <v>44624.325347999998</v>
       </c>
-      <c r="R13" s="22">
+      <c r="Y13" s="20">
         <v>8.7023620000000008</v>
       </c>
-      <c r="S13" s="22">
+      <c r="Z13" s="20">
         <v>4.2089480000000004</v>
       </c>
-      <c r="T13" s="22">
+      <c r="AA13" s="20">
         <v>51.717542999999999</v>
       </c>
-      <c r="W13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="X13" s="12">
-        <v>44624.325347999998</v>
-      </c>
-      <c r="Y13" s="21">
-        <v>8.7023620000000008</v>
-      </c>
-      <c r="Z13" s="21">
-        <v>4.2089480000000004</v>
-      </c>
-      <c r="AA13" s="21">
-        <v>51.717542999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="I14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="8">
         <f>AVERAGE(Table1[Max Rate (Cases)])</f>
-        <v>44147.599585199991</v>
+        <v>31417.435401100003</v>
       </c>
       <c r="K14" s="9">
         <f>AVERAGE(Table1[Half-Width (Weeks)])</f>
@@ -2229,38 +2272,38 @@
         <f>AVERAGE(Table1[Max Week])</f>
         <v>51.307538600000001</v>
       </c>
-      <c r="P14" s="18" t="s">
+      <c r="P14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="26">
+      <c r="Q14" s="25">
         <f>AVERAGE(Q4:Q13)</f>
-        <v>44147.599585199991</v>
-      </c>
-      <c r="R14" s="27">
+        <v>31417.435401100003</v>
+      </c>
+      <c r="R14" s="26">
         <f t="shared" ref="R14:T14" si="3">AVERAGE(R4:R13)</f>
         <v>10.198203000000001</v>
       </c>
-      <c r="S14" s="27">
+      <c r="S14" s="26">
         <f t="shared" si="3"/>
         <v>4.9324200999999999</v>
       </c>
-      <c r="T14" s="28">
+      <c r="T14" s="27">
         <f t="shared" si="3"/>
         <v>51.307538600000001</v>
       </c>
-      <c r="W14" s="18"/>
-      <c r="X14" s="26"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="28"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W14" s="17"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="27"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>31</v>
       </c>
       <c r="J15" s="10">
         <f>STDEV(Table1[Max Rate (Cases)])</f>
-        <v>4772.5582616910733</v>
+        <v>3396.3690504914489</v>
       </c>
       <c r="K15" s="1">
         <f>STDEV(Table1[Half-Width (Weeks)])</f>
@@ -2274,32 +2317,32 @@
         <f>STDEV(Table1[Max Week])</f>
         <v>0.81178335067446938</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="P15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="18">
         <f>STDEV(Q4:Q13)</f>
-        <v>4772.5582616910733</v>
-      </c>
-      <c r="R15" s="24">
+        <v>3396.3690504914489</v>
+      </c>
+      <c r="R15" s="23">
         <f t="shared" ref="R15:T15" si="4">STDEV(R4:R13)</f>
         <v>1.1177553550416162</v>
       </c>
-      <c r="S15" s="24">
+      <c r="S15" s="23">
         <f t="shared" si="4"/>
         <v>0.54060872713028429</v>
       </c>
-      <c r="T15" s="23">
+      <c r="T15" s="22">
         <f t="shared" si="4"/>
         <v>0.81178335067446938</v>
       </c>
-      <c r="W15" s="18"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="23"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W15" s="17"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="22"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2311,7 +2354,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -2342,28 +2385,28 @@
       <c r="M17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="25" t="s">
+      <c r="P17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="R17" s="25" t="s">
+      <c r="R17" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="S17" s="25" t="s">
+      <c r="S17" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="T17" s="25" t="s">
+      <c r="T17" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -2387,7 +2430,7 @@
       </c>
       <c r="J18" s="5">
         <f>B18*$B$1</f>
-        <v>45246.886272000003</v>
+        <v>32199.737696</v>
       </c>
       <c r="K18" s="1">
         <v>4.9343019999999997</v>
@@ -2399,29 +2442,29 @@
         <f>D18+30</f>
         <v>52.329311000000004</v>
       </c>
-      <c r="P18" s="14" t="s">
+      <c r="P18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="14">
         <f>B18*$B$1</f>
-        <v>45246.886272000003</v>
-      </c>
-      <c r="R18" s="20">
+        <v>32199.737696</v>
+      </c>
+      <c r="R18" s="19">
         <v>4.9343019999999997</v>
       </c>
-      <c r="S18" s="20">
+      <c r="S18" s="19">
         <v>3.924741</v>
       </c>
-      <c r="T18" s="20">
+      <c r="T18" s="19">
         <v>52.329311000000004</v>
       </c>
-      <c r="W18" s="14"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W18" s="13"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -2445,7 +2488,7 @@
       </c>
       <c r="J19" s="5">
         <f t="shared" ref="J19:J27" si="5">B19*$B$1</f>
-        <v>63308.796371999997</v>
+        <v>45053.412620999996</v>
       </c>
       <c r="K19" s="1">
         <v>7.0817410000000001</v>
@@ -2457,29 +2500,29 @@
         <f t="shared" ref="M19:M27" si="6">D19+30</f>
         <v>52.030391999999999</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="P19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="11">
         <f t="shared" ref="Q19:Q27" si="7">B19*$B$1</f>
-        <v>63308.796371999997</v>
-      </c>
-      <c r="R19" s="21">
+        <v>45053.412620999996</v>
+      </c>
+      <c r="R19" s="20">
         <v>7.0817410000000001</v>
       </c>
-      <c r="S19" s="21">
+      <c r="S19" s="20">
         <v>5.6328120000000004</v>
       </c>
-      <c r="T19" s="21">
+      <c r="T19" s="20">
         <v>52.030391999999999</v>
       </c>
-      <c r="W19" s="13"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W19" s="12"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -2503,7 +2546,7 @@
       </c>
       <c r="J20" s="5">
         <f t="shared" si="5"/>
-        <v>65972.027375999998</v>
+        <v>46948.688668000003</v>
       </c>
       <c r="K20" s="1">
         <v>5.1457280000000001</v>
@@ -2515,29 +2558,29 @@
         <f t="shared" si="6"/>
         <v>50.619607999999999</v>
       </c>
-      <c r="P20" s="13" t="s">
+      <c r="P20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="11">
         <f t="shared" si="7"/>
-        <v>65972.027375999998</v>
-      </c>
-      <c r="R20" s="21">
+        <v>46948.688668000003</v>
+      </c>
+      <c r="R20" s="20">
         <v>5.1457280000000001</v>
       </c>
-      <c r="S20" s="21">
+      <c r="S20" s="20">
         <v>4.0929089999999997</v>
       </c>
-      <c r="T20" s="21">
+      <c r="T20" s="20">
         <v>50.619607999999999</v>
       </c>
-      <c r="W20" s="13"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W20" s="12"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2561,7 +2604,7 @@
       </c>
       <c r="J21" s="5">
         <f t="shared" si="5"/>
-        <v>69146.530956000002</v>
+        <v>49207.809482999997</v>
       </c>
       <c r="K21" s="1">
         <v>7.2621359999999999</v>
@@ -2573,29 +2616,29 @@
         <f t="shared" si="6"/>
         <v>52.438113999999999</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="P21" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="Q21" s="11">
         <f t="shared" si="7"/>
-        <v>69146.530956000002</v>
-      </c>
-      <c r="R21" s="21">
+        <v>49207.809482999997</v>
+      </c>
+      <c r="R21" s="20">
         <v>7.2621359999999999</v>
       </c>
-      <c r="S21" s="21">
+      <c r="S21" s="20">
         <v>5.7762979999999997</v>
       </c>
-      <c r="T21" s="21">
+      <c r="T21" s="20">
         <v>52.438113999999999</v>
       </c>
-      <c r="W21" s="13"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W21" s="12"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -2619,7 +2662,7 @@
       </c>
       <c r="J22" s="5">
         <f t="shared" si="5"/>
-        <v>54732.042359999999</v>
+        <v>38949.805229999998</v>
       </c>
       <c r="K22" s="1">
         <v>6.9867920000000003</v>
@@ -2631,29 +2674,29 @@
         <f t="shared" si="6"/>
         <v>52.524986999999996</v>
       </c>
-      <c r="P22" s="13" t="s">
+      <c r="P22" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="11">
         <f t="shared" si="7"/>
-        <v>54732.042359999999</v>
-      </c>
-      <c r="R22" s="21">
+        <v>38949.805229999998</v>
+      </c>
+      <c r="R22" s="20">
         <v>6.9867920000000003</v>
       </c>
-      <c r="S22" s="21">
+      <c r="S22" s="20">
         <v>5.5572900000000001</v>
       </c>
-      <c r="T22" s="21">
+      <c r="T22" s="20">
         <v>52.524986999999996</v>
       </c>
-      <c r="W22" s="13"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W22" s="12"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2677,7 +2720,7 @@
       </c>
       <c r="J23" s="5">
         <f t="shared" si="5"/>
-        <v>84867.978492000009</v>
+        <v>60395.905031000002</v>
       </c>
       <c r="K23" s="1">
         <v>6.0841279999999998</v>
@@ -2689,29 +2732,29 @@
         <f t="shared" si="6"/>
         <v>50.507648000000003</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="P23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="11">
         <f t="shared" si="7"/>
-        <v>84867.978492000009</v>
-      </c>
-      <c r="R23" s="21">
+        <v>60395.905031000002</v>
+      </c>
+      <c r="R23" s="20">
         <v>6.0841279999999998</v>
       </c>
-      <c r="S23" s="21">
+      <c r="S23" s="20">
         <v>4.8393110000000004</v>
       </c>
-      <c r="T23" s="21">
+      <c r="T23" s="20">
         <v>50.507648000000003</v>
       </c>
-      <c r="W23" s="13"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="21"/>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="21"/>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W23" s="12"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2735,7 +2778,7 @@
       </c>
       <c r="J24" s="5">
         <f t="shared" si="5"/>
-        <v>65459.373480000002</v>
+        <v>46583.860889999996</v>
       </c>
       <c r="K24" s="1">
         <v>7.9179510000000004</v>
@@ -2747,29 +2790,29 @@
         <f t="shared" si="6"/>
         <v>51.984837999999996</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="P24" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="11">
         <f t="shared" si="7"/>
-        <v>65459.373480000002</v>
-      </c>
-      <c r="R24" s="21">
+        <v>46583.860889999996</v>
+      </c>
+      <c r="R24" s="20">
         <v>7.9179510000000004</v>
       </c>
-      <c r="S24" s="21">
+      <c r="S24" s="20">
         <v>6.2979329999999996</v>
       </c>
-      <c r="T24" s="21">
+      <c r="T24" s="20">
         <v>51.984837999999996</v>
       </c>
-      <c r="W24" s="13"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="21"/>
-      <c r="AA24" s="21"/>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W24" s="12"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2793,7 +2836,7 @@
       </c>
       <c r="J25" s="5">
         <f t="shared" si="5"/>
-        <v>71774.169947999995</v>
+        <v>51077.756638999999</v>
       </c>
       <c r="K25" s="1">
         <v>5.481414</v>
@@ -2805,29 +2848,29 @@
         <f t="shared" si="6"/>
         <v>51.186745000000002</v>
       </c>
-      <c r="P25" s="13" t="s">
+      <c r="P25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="Q25" s="11">
         <f t="shared" si="7"/>
-        <v>71774.169947999995</v>
-      </c>
-      <c r="R25" s="21">
+        <v>51077.756638999999</v>
+      </c>
+      <c r="R25" s="20">
         <v>5.481414</v>
       </c>
-      <c r="S25" s="21">
+      <c r="S25" s="20">
         <v>4.3599129999999997</v>
       </c>
-      <c r="T25" s="21">
+      <c r="T25" s="20">
         <v>51.186745000000002</v>
       </c>
-      <c r="W25" s="13"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W25" s="12"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -2851,7 +2894,7 @@
       </c>
       <c r="J26" s="5">
         <f t="shared" si="5"/>
-        <v>67514.409287999995</v>
+        <v>48046.317633999999</v>
       </c>
       <c r="K26" s="1">
         <v>6.7356749999999996</v>
@@ -2863,29 +2906,29 @@
         <f t="shared" si="6"/>
         <v>51.122333999999995</v>
       </c>
-      <c r="P26" s="13" t="s">
+      <c r="P26" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="Q26" s="11">
         <f t="shared" si="7"/>
-        <v>67514.409287999995</v>
-      </c>
-      <c r="R26" s="21">
+        <v>48046.317633999999</v>
+      </c>
+      <c r="R26" s="20">
         <v>6.7356749999999996</v>
       </c>
-      <c r="S26" s="21">
+      <c r="S26" s="20">
         <v>5.3575520000000001</v>
       </c>
-      <c r="T26" s="21">
+      <c r="T26" s="20">
         <v>51.122333999999995</v>
       </c>
-      <c r="W26" s="13"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-    </row>
-    <row r="27" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W26" s="12"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+    </row>
+    <row r="27" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -2909,7 +2952,7 @@
       </c>
       <c r="J27" s="5">
         <f t="shared" si="5"/>
-        <v>69237.559943999993</v>
+        <v>49272.589841999994</v>
       </c>
       <c r="K27" s="1">
         <v>7.0461600000000004</v>
@@ -2921,35 +2964,35 @@
         <f t="shared" si="6"/>
         <v>51.900856000000005</v>
       </c>
-      <c r="P27" s="16" t="s">
+      <c r="P27" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="16">
         <f t="shared" si="7"/>
-        <v>69237.559943999993</v>
-      </c>
-      <c r="R27" s="22">
+        <v>49272.589841999994</v>
+      </c>
+      <c r="R27" s="21">
         <v>7.0461600000000004</v>
       </c>
-      <c r="S27" s="22">
+      <c r="S27" s="21">
         <v>5.6045119999999997</v>
       </c>
-      <c r="T27" s="22">
+      <c r="T27" s="21">
         <v>51.900856000000005</v>
       </c>
-      <c r="W27" s="16"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="22"/>
-      <c r="AA27" s="22"/>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W27" s="15"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="21"/>
+      <c r="AA27" s="21"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="I28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="J28" s="8">
         <f>AVERAGE(Table14[Max Rate (Cases)])</f>
-        <v>65725.977448799997</v>
+        <v>46773.588373399994</v>
       </c>
       <c r="K28" s="9">
         <f>AVERAGE(Table14[Half-Width (Weeks)])</f>
@@ -2963,38 +3006,38 @@
         <f>AVERAGE(Table14[Max Week])</f>
         <v>51.664483299999993</v>
       </c>
-      <c r="P28" s="18" t="s">
+      <c r="P28" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q28" s="26">
+      <c r="Q28" s="25">
         <f>AVERAGE(Q18:Q27)</f>
-        <v>65725.977448799997</v>
-      </c>
-      <c r="R28" s="27">
+        <v>46773.588373399994</v>
+      </c>
+      <c r="R28" s="26">
         <f t="shared" ref="R28" si="8">AVERAGE(R18:R27)</f>
         <v>6.4676027000000005</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="26">
         <f t="shared" ref="S28" si="9">AVERAGE(S18:S27)</f>
         <v>5.1443270999999999</v>
       </c>
-      <c r="T28" s="28">
+      <c r="T28" s="27">
         <f t="shared" ref="T28" si="10">AVERAGE(T18:T27)</f>
         <v>51.664483299999993</v>
       </c>
-      <c r="W28" s="18"/>
-      <c r="X28" s="26"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="28"/>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W28" s="17"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="27"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="I29" t="s">
         <v>31</v>
       </c>
       <c r="J29" s="10">
         <f>STDEV(Table14[Max Rate (Cases)])</f>
-        <v>10416.124730277312</v>
+        <v>7412.5870696941683</v>
       </c>
       <c r="K29" s="1">
         <f>STDEV(Table14[Half-Width (Weeks)])</f>
@@ -3008,32 +3051,32 @@
         <f>STDEV(Table14[Max Week])</f>
         <v>0.7472577543473421</v>
       </c>
-      <c r="P29" s="18" t="s">
+      <c r="P29" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="Q29" s="19">
+      <c r="Q29" s="18">
         <f>STDEV(Q18:Q27)</f>
-        <v>10416.124730277312</v>
-      </c>
-      <c r="R29" s="24">
+        <v>7412.5870696941683</v>
+      </c>
+      <c r="R29" s="23">
         <f t="shared" ref="R29:T29" si="11">STDEV(R18:R27)</f>
         <v>1.0003384316743371</v>
       </c>
-      <c r="S29" s="24">
+      <c r="S29" s="23">
         <f t="shared" si="11"/>
         <v>0.7956684976443722</v>
       </c>
-      <c r="T29" s="23">
+      <c r="T29" s="22">
         <f t="shared" si="11"/>
         <v>0.7472577543473421</v>
       </c>
-      <c r="W29" s="18"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="23"/>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="W29" s="17"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="23"/>
+      <c r="Z29" s="23"/>
+      <c r="AA29" s="22"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>45</v>
       </c>
@@ -3056,11 +3099,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>0.83205119999999999</v>
       </c>
       <c r="C32">
@@ -3069,7 +3112,7 @@
       <c r="D32">
         <v>13.658386999999999</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="28">
         <v>-2.3639699999999999E-17</v>
       </c>
       <c r="F32">
@@ -3082,11 +3125,11 @@
         <v>3.6482000000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="28">
         <v>0.79006240000000005</v>
       </c>
       <c r="C33">
@@ -3095,7 +3138,7 @@
       <c r="D33">
         <v>17.031714000000001</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="28">
         <v>0.31906299999999999</v>
       </c>
       <c r="F33">
@@ -3108,269 +3151,269 @@
         <v>1.9481999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="J34" s="34" t="s">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J34" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="K34" s="34"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="J35" s="39" t="s">
+      <c r="K34" s="37"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J35" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="K35" s="39" t="s">
+      <c r="K35" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="I36" s="31" t="s">
+    <row r="36" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="I36" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="33">
         <f>B32*$B$1</f>
-        <v>38310.965452800003</v>
-      </c>
-      <c r="K36" s="35">
+        <v>27263.821670400001</v>
+      </c>
+      <c r="K36" s="33">
         <f>B33*$B$1</f>
-        <v>36377.633145600004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+        <v>25887.974660800002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="I37" t="s">
         <v>54</v>
       </c>
-      <c r="J37" s="33">
+      <c r="J37" s="32">
         <f>D32+35</f>
         <v>48.658386999999998</v>
       </c>
-      <c r="K37" s="33">
+      <c r="K37" s="32">
         <f>D33+35</f>
         <v>52.031714000000001</v>
       </c>
-      <c r="P37" s="31" t="s">
+      <c r="P37" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-    </row>
-    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="I38" s="38" t="s">
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+    </row>
+    <row r="38" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="I38" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="32">
         <v>5.6545860000000001</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="32">
         <v>3.7615189999999998</v>
       </c>
-      <c r="P38" s="30" t="s">
+      <c r="P38" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="Q38" s="12">
+      <c r="Q38" s="11">
         <v>47528.734823999999</v>
       </c>
-      <c r="R38" s="21">
+      <c r="R38" s="20">
         <v>10.818647</v>
       </c>
-      <c r="S38" s="21">
+      <c r="S38" s="20">
         <v>5.2325020000000002</v>
       </c>
-      <c r="T38" s="21">
+      <c r="T38" s="20">
         <v>51.546239</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="I39" s="37" t="s">
+    <row r="39" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="I39" t="s">
         <v>58</v>
       </c>
       <c r="J39" s="10">
         <f>-2.36397E-17*B1</f>
-        <v>-1.0884663467999999E-12</v>
+        <v>-7.7460204989999993E-13</v>
       </c>
       <c r="K39" s="10">
         <f>0.319063*B1</f>
-        <v>14690.936771999999</v>
-      </c>
-      <c r="P39" s="30" t="s">
+        <v>10454.737320999999</v>
+      </c>
+      <c r="P39" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="Q39" s="12">
+      <c r="Q39" s="11">
         <v>38775.033719999999</v>
       </c>
-      <c r="R39" s="21">
+      <c r="R39" s="20">
         <v>11.514607</v>
       </c>
-      <c r="S39" s="21">
+      <c r="S39" s="20">
         <v>5.5691059999999997</v>
       </c>
-      <c r="T39" s="21">
+      <c r="T39" s="20">
         <v>51.825242000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="I40" t="s">
         <v>57</v>
       </c>
-      <c r="J40" s="33">
+      <c r="J40" s="32">
         <f>G32+35 - 52</f>
         <v>8.2525249999999986</v>
       </c>
-      <c r="K40" s="33">
+      <c r="K40" s="32">
         <f>G33+35-52</f>
         <v>7.317537999999999</v>
       </c>
-      <c r="P40" s="30" t="s">
+      <c r="P40" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="Q40" s="12">
+      <c r="Q40" s="11">
         <v>43605.141407999996</v>
       </c>
-      <c r="R40" s="21">
+      <c r="R40" s="20">
         <v>9.4750730000000001</v>
       </c>
-      <c r="S40" s="21">
+      <c r="S40" s="20">
         <v>4.5826739999999999</v>
       </c>
-      <c r="T40" s="21">
+      <c r="T40" s="20">
         <v>50.648973999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="I41" s="36" t="s">
+    <row r="41" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="I41" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="32">
         <v>19.669132000000001</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="32">
         <v>10.349474000000001</v>
       </c>
-      <c r="P41" s="30" t="s">
+      <c r="P41" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="Q41" s="12">
+      <c r="Q41" s="11">
         <v>42441.333264000001</v>
       </c>
-      <c r="R41" s="21">
+      <c r="R41" s="20">
         <v>8.7152670000000008</v>
       </c>
-      <c r="S41" s="21">
+      <c r="S41" s="20">
         <v>4.2151899999999998</v>
       </c>
-      <c r="T41" s="21">
+      <c r="T41" s="20">
         <v>52.646534000000003</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="I42" s="36" t="s">
+    <row r="42" spans="1:20" ht="18" x14ac:dyDescent="0.35">
+      <c r="I42" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="31">
         <v>2.0699999999999998</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="31">
         <v>1.26</v>
       </c>
-      <c r="P42" s="30" t="s">
+      <c r="P42" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="Q42" s="12">
+      <c r="Q42" s="11">
         <v>43653.625739999996</v>
       </c>
-      <c r="R42" s="21">
+      <c r="R42" s="20">
         <v>9.8766829999999999</v>
       </c>
-      <c r="S42" s="21">
+      <c r="S42" s="20">
         <v>4.7769149999999998</v>
       </c>
-      <c r="T42" s="21">
+      <c r="T42" s="20">
         <v>51.607849999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="P43" s="30" t="s">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P43" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="Q43" s="12">
+      <c r="Q43" s="11">
         <v>53244.038412000002</v>
       </c>
-      <c r="R43" s="21">
+      <c r="R43" s="20">
         <v>11.655272999999999</v>
       </c>
-      <c r="S43" s="21">
+      <c r="S43" s="20">
         <v>5.6371399999999996</v>
       </c>
-      <c r="T43" s="21">
+      <c r="T43" s="20">
         <v>50.418517000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="P44" s="30" t="s">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P44" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="Q44" s="12">
+      <c r="Q44" s="11">
         <v>37300.336488000001</v>
       </c>
-      <c r="R44" s="21">
+      <c r="R44" s="20">
         <v>9.9486910000000002</v>
       </c>
-      <c r="S44" s="21">
+      <c r="S44" s="20">
         <v>4.8117419999999997</v>
       </c>
-      <c r="T44" s="21">
+      <c r="T44" s="20">
         <v>51.911073000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="P45" s="30" t="s">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P45" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="Q45" s="12">
+      <c r="Q45" s="11">
         <v>41319.240984000004</v>
       </c>
-      <c r="R45" s="21">
+      <c r="R45" s="20">
         <v>11.50141</v>
       </c>
-      <c r="S45" s="21">
+      <c r="S45" s="20">
         <v>5.5627240000000002</v>
       </c>
-      <c r="T45" s="21">
+      <c r="T45" s="20">
         <v>50.035004999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="P46" s="30" t="s">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P46" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="Q46" s="12">
+      <c r="Q46" s="11">
         <v>48984.185663999997</v>
       </c>
-      <c r="R46" s="21">
+      <c r="R46" s="20">
         <v>9.7740170000000006</v>
       </c>
-      <c r="S46" s="21">
+      <c r="S46" s="20">
         <v>4.7272600000000002</v>
       </c>
-      <c r="T46" s="21">
+      <c r="T46" s="20">
         <v>50.718409000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="P47" s="30" t="s">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P47" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="Q47" s="12">
+      <c r="Q47" s="11">
         <v>44624.325347999998</v>
       </c>
-      <c r="R47" s="21">
+      <c r="R47" s="20">
         <v>8.7023620000000008</v>
       </c>
-      <c r="S47" s="21">
+      <c r="S47" s="20">
         <v>4.2089480000000004</v>
       </c>
-      <c r="T47" s="21">
+      <c r="T47" s="20">
         <v>51.717542999999999</v>
       </c>
     </row>
@@ -3384,4 +3427,154 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD488FD-815C-46D7-A15A-47C5B9C4A1EC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF28E9D-8542-45E8-8788-6A7386959AD3}">
+  <dimension ref="A2:C17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>AVERAGE(B3:B17)</f>
+        <v>42.866666666666667</v>
+      </c>
+      <c r="C2">
+        <f>STDEV(B3:B17)</f>
+        <v>11.41969893690389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>